--- a/backend/data/DSA1101_Sem1_2425_Midterm.xlsx
+++ b/backend/data/DSA1101_Sem1_2425_Midterm.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0707AD-D48B-0E47-972E-7358332ECD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7092195-D50A-D54A-B1C6-269ADDFAC719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16660" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="70">
-  <si>
-    <t>Context ID</t>
-  </si>
   <si>
     <t>Context Text</t>
   </si>
@@ -395,6 +392,9 @@
   </si>
   <si>
     <t>Sub-Question Number</t>
+  </si>
+  <si>
+    <t>Context ID</t>
   </si>
 </sst>
 </file>
@@ -785,13 +785,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="238" x14ac:dyDescent="0.2">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="85" x14ac:dyDescent="0.2">
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -833,52 +833,52 @@
   <sheetData>
     <row r="1" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" t="s">
-        <v>69</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -892,22 +892,22 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M2">
         <v>2</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -921,22 +921,22 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3">
         <v>2</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -950,22 +950,22 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M4">
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -979,22 +979,22 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M5">
         <v>2</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -1008,22 +1008,22 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M6">
         <v>4</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1037,22 +1037,22 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1066,22 +1066,22 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M8">
         <v>4</v>
       </c>
       <c r="N8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1095,22 +1095,22 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1124,22 +1124,22 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M10">
         <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -1153,22 +1153,22 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" t="s">
         <v>44</v>
       </c>
-      <c r="K11" t="s">
-        <v>45</v>
-      </c>
       <c r="M11">
         <v>2</v>
       </c>
       <c r="N11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="409" customHeight="1" x14ac:dyDescent="0.2">
@@ -1182,22 +1182,22 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M12">
         <v>4</v>
       </c>
       <c r="N12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -1211,22 +1211,22 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -1240,22 +1240,22 @@
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M14">
         <v>2</v>
       </c>
       <c r="N14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -1269,22 +1269,22 @@
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M15">
         <v>2</v>
       </c>
       <c r="N15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="409" customHeight="1" x14ac:dyDescent="0.2">
@@ -1298,23 +1298,23 @@
         <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H16" s="1"/>
       <c r="K16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M16">
         <v>6</v>
       </c>
       <c r="N16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="68" x14ac:dyDescent="0.2">
@@ -1328,22 +1328,22 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M17">
         <v>5</v>
       </c>
       <c r="N17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="85" x14ac:dyDescent="0.2">
@@ -1357,22 +1357,22 @@
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
